--- a/Full_DGA_Report.xlsx
+++ b/Full_DGA_Report.xlsx
@@ -95,7 +95,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -144,6 +144,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
@@ -174,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -242,10 +247,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -325,6 +333,91 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="16259175" cy="11649075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="20393025" cy="8391525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11887200" cy="10858500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1308,12 +1401,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Insufficient gas for reliable Duval analysis</t>
+          <t>High Energy Discharge (Arc)</t>
         </is>
       </c>
     </row>
@@ -1322,6 +1415,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2028,12 +2122,12 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>NORMAL — Insufficient gas for reliable Duval analysis</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Normal</t>
+          <t>D2 — High Energy Discharge (Arc)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2097,7 +2191,7 @@
           <t>Discharge of High Energy (arcing)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -2119,7 +2213,7 @@
           <t>CO dominant — Thermal fault involving cellulose (paper/pressboard overheating)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2175,9 +2269,9 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>OVERALL ASSESSMENT:  MODERATE  (Severity Index = 0.50)</t>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>OVERALL ASSESSMENT:  CRITICAL  (Severity Index = 0.85)</t>
         </is>
       </c>
     </row>
@@ -2187,5 +2281,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>